--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487764_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487764_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.056</v>
+        <v>2.6023</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3275</v>
+        <v>2.8151</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2715</v>
+        <v>-0.2128</v>
       </c>
       <c r="G2" t="n">
         <v>2.0024</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0235</v>
+        <v>-0.4303</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5525</v>
+        <v>0.0401</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5291</v>
+        <v>-0.4703</v>
       </c>
       <c r="V2" t="n">
         <v>1.2383</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3996</v>
+        <v>-0.1266</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1648</v>
+        <v>0.0495</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2348</v>
+        <v>-0.1761</v>
       </c>
       <c r="G3" t="n">
         <v>0.8752</v>
@@ -688,13 +688,13 @@
         <v>0.4162</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6505</v>
+        <v>-0.3774</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.259</v>
+        <v>-0.2003</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.523</v>
+        <v>-0.5863</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3057</v>
+        <v>1.1196</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2173</v>
+        <v>-1.7058</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3357</v>
+        <v>-0.3798</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6035</v>
+        <v>-0.8549</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2678</v>
+        <v>0.4752</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3442</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1875</v>
+        <v>1.9868</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1568</v>
+        <v>-1.0638</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0085</v>
+        <v>-1.3027</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5839</v>
+        <v>-2.8417</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4245</v>
+        <v>1.539</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8731</v>
+        <v>1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.3299</v>
+        <v>-0.2081</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2864</v>
+        <v>-1.2658</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1338</v>
+        <v>-0.179</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1526</v>
+        <v>-1.0868</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3007</v>
+        <v>-0.8137</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8137</v>
+        <v>0.5838</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.513</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1319</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1709</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.039</v>
+        <v>-0.3347</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1679</v>
+        <v>1.3357</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0554</v>
+        <v>1.6035</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8875</v>
+        <v>-0.2678</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.127</v>
+        <v>2.3442</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3328</v>
+        <v>2.1875</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2058</v>
+        <v>0.1568</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0409</v>
+        <v>-1.0085</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2775</v>
+        <v>-0.5839</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3184</v>
+        <v>-0.4245</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6244</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4104</v>
+        <v>-0.6601</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0033</v>
+        <v>-0.39</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4071</v>
+        <v>-0.2701</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0708</v>
+        <v>0.3007</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0708</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2079</v>
+        <v>-1.4072</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7329</v>
+        <v>-1.5342</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9407</v>
+        <v>0.1271</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3798</v>
+        <v>-0.1679</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8549</v>
+        <v>-1.0554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4752</v>
+        <v>0.8875</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9229000000000001</v>
+        <v>-0.127</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9868</v>
+        <v>-1.3328</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0638</v>
+        <v>1.2058</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3027</v>
+        <v>-0.0409</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.8417</v>
+        <v>0.2775</v>
       </c>
       <c r="O6" t="n">
-        <v>1.539</v>
+        <v>-0.3184</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8731</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8874</v>
+        <v>-0.6857</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5657</v>
+        <v>-0.3667</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3217</v>
+        <v>-0.319</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8137</v>
+        <v>0.0708</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3912</v>
+        <v>-1.4941</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8766</v>
+        <v>-2.0676</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4854</v>
+        <v>0.5735</v>
       </c>
       <c r="G7" t="n">
         <v>-2.5276</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5285</v>
+        <v>-0.6314</v>
       </c>
       <c r="T7" t="n">
-        <v>0.422</v>
+        <v>0.231</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9505</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1213</v>
+        <v>-3.106</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6781</v>
+        <v>-1.3986</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4431</v>
+        <v>-1.7074</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3925</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3562</v>
+        <v>-0.3409</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1534</v>
+        <v>-0.1109</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7076</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4399</v>
+        <v>-3.1412</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3995</v>
+        <v>-4.0128</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9597</v>
+        <v>0.8716</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2525</v>
@@ -1156,13 +1156,13 @@
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7607</v>
+        <v>-0.4621</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.2901</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6641</v>
+        <v>-0.7522</v>
       </c>
       <c r="V9" t="n">
         <v>0.0708</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9641</v>
+        <v>-4.603</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9358</v>
+        <v>-2.7215</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0283</v>
+        <v>-1.8815</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4555</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4118</v>
+        <v>-1.0507</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5473</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0968</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0167</v>
+        <v>-6.7283</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6153</v>
+        <v>-5.1215</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4013</v>
+        <v>-1.6069</v>
       </c>
       <c r="G11" t="n">
         <v>-5.6316</v>
@@ -1312,13 +1312,13 @@
         <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.28</v>
+        <v>-0.9917</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4228</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8572</v>
+        <v>-1.0627</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9376</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.1396</v>
+        <v>-19.4871</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.0863</v>
+        <v>-13.434</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.0529</v>
+        <v>-6.052999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-7.594099999999999</v>
@@ -1363,7 +1363,7 @@
         <v>3.2045</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2230000000000008</v>
+        <v>-0.2230000000000016</v>
       </c>
       <c r="K12" t="n">
         <v>2.492</v>
@@ -1378,7 +1378,7 @@
         <v>-13.2903</v>
       </c>
       <c r="O12" t="n">
-        <v>5.9192</v>
+        <v>5.919200000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-3.1218</v>
@@ -1390,13 +1390,13 @@
         <v>13.5276</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.5484</v>
+        <v>-6.8961</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8665</v>
+        <v>-1.214</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.681999999999999</v>
+        <v>-5.682</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8751</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.3811</v>
+        <v>6.6675</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1876</v>
+        <v>3.6874</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1935</v>
+        <v>2.9802</v>
       </c>
       <c r="G13" t="n">
         <v>1.912</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7396</v>
+        <v>2.0261</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6585</v>
+        <v>1.1583</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0811</v>
+        <v>0.8678</v>
       </c>
       <c r="V13" t="n">
         <v>2.1051</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.718</v>
+        <v>6.2805</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1345</v>
+        <v>3.0629</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5835</v>
+        <v>3.2176</v>
       </c>
       <c r="G14" t="n">
         <v>3.9723</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2025</v>
+        <v>1.7651</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3479</v>
+        <v>1.2764</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1454</v>
+        <v>0.4887</v>
       </c>
       <c r="V14" t="n">
         <v>1.1675</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2164</v>
+        <v>3.6283</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4404</v>
+        <v>0.7975</v>
       </c>
       <c r="F15" t="n">
-        <v>2.776</v>
+        <v>2.8308</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9461000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>1.892</v>
+        <v>1.3038</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5807</v>
+        <v>0.9378</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3113</v>
+        <v>0.3661</v>
       </c>
       <c r="V15" t="n">
         <v>1.3975</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9775</v>
+        <v>3.1729</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4221</v>
+        <v>0.5423</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3997</v>
+        <v>2.6306</v>
       </c>
       <c r="G16" t="n">
         <v>0.4621</v>
@@ -1702,13 +1702,13 @@
         <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5252</v>
+        <v>0.6702</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6277</v>
+        <v>0.3367</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1025</v>
+        <v>0.3334</v>
       </c>
       <c r="V16" t="n">
         <v>0.5838</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.752</v>
+        <v>2.7712</v>
       </c>
       <c r="E17" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.9732</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7432</v>
+        <v>1.798</v>
       </c>
       <c r="G17" t="n">
         <v>0.922</v>
@@ -1780,13 +1780,13 @@
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6674</v>
+        <v>0.3518</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6277</v>
+        <v>0.3367</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0397</v>
+        <v>0.0151</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5838</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9268</v>
+        <v>2.4999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0364</v>
+        <v>1.0008</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8904</v>
+        <v>1.4991</v>
       </c>
       <c r="G18" t="n">
         <v>3.8675</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8377</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6524</v>
+        <v>0.312</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1852</v>
+        <v>0.4235</v>
       </c>
       <c r="V18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7464</v>
+        <v>1.9559</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4149</v>
+        <v>2.8435</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6685</v>
+        <v>-0.8875</v>
       </c>
       <c r="G19" t="n">
         <v>2.061</v>
@@ -1936,13 +1936,13 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3771</v>
+        <v>0.8325</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0033</v>
+        <v>0.4253</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3738</v>
+        <v>0.4071</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9376</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.154</v>
+        <v>-1.8278</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.935</v>
+        <v>-2.2565</v>
       </c>
       <c r="F20" t="n">
-        <v>0.781</v>
+        <v>0.4286</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2386</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4581</v>
+        <v>0.7844</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4658</v>
+        <v>0.1443</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="V20" t="n">
         <v>0.7076</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4247</v>
+        <v>-2.8659</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8123</v>
+        <v>-4.598</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3876</v>
+        <v>1.7321</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4181</v>
@@ -2092,13 +2092,13 @@
         <v>2.7055</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6635</v>
+        <v>1.2223</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5401</v>
+        <v>0.7544</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1234</v>
+        <v>0.4678</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3351</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>20.1395</v>
+        <v>22.2825</v>
       </c>
       <c r="E22" t="n">
-        <v>6.053199999999999</v>
+        <v>6.0531</v>
       </c>
       <c r="F22" t="n">
-        <v>14.0864</v>
+        <v>16.2295</v>
       </c>
       <c r="G22" t="n">
         <v>7.5941</v>
@@ -2170,13 +2170,13 @@
         <v>16.6494</v>
       </c>
       <c r="S22" t="n">
-        <v>7.548299999999999</v>
+        <v>9.691600000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>5.6819</v>
+        <v>5.681900000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8666</v>
+        <v>4.0095</v>
       </c>
       <c r="V22" t="n">
         <v>1.875</v>
